--- a/currentbuild/StructureDefinition-auditevent-encounter.xlsx
+++ b/currentbuild/StructureDefinition-auditevent-encounter.xlsx
@@ -24,13 +24,13 @@
     <t>URL</t>
   </si>
   <si>
-    <t>urn:no-basis-auditevent/StructureDefinition/auditevent-encounter</t>
+    <t>http://hl7.no/fhir/StructureDefinition/auditevent-encounter</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.2</t>
+    <t>2.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-28T16:36:28+00:00</t>
+    <t>2024-06-04T05:44:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -745,7 +745,7 @@
     <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
   </si>
   <si>
-    <t>urn:no-basis-auditevent/ValueSet/no-basis-encounter-auditevent-servicetype</t>
+    <t>http://hl7.no/fhir/ValueSet/no-basis-encounter-auditevent-servicetype</t>
   </si>
   <si>
     <t>CodeableConcept.coding</t>
@@ -1522,7 +1522,7 @@
     <t>Encounter.location.location</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(urn:no-basis-auditevent/StructureDefinition/auditevent-encounter-pointofcare)
+    <t xml:space="preserve">Reference(http://hl7.no/fhir/StructureDefinition/auditevent-encounter-pointofcare)
 </t>
   </si>
   <si>
@@ -1593,7 +1593,7 @@
     <t>Encounter.serviceProvider</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(urn:no-basis-auditevent/StructureDefinition/auditevent-encounter-serviceprovider-organization)
+    <t xml:space="preserve">Reference(http://hl7.no/fhir/StructureDefinition/auditevent-encounter-serviceprovider-organization)
 </t>
   </si>
   <si>
@@ -1937,7 +1937,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="99.32421875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="92.42578125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1952,7 +1952,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="74.65625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="71.91796875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="65.01953125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>

--- a/currentbuild/StructureDefinition-auditevent-encounter.xlsx
+++ b/currentbuild/StructureDefinition-auditevent-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T05:44:14+00:00</t>
+    <t>2024-06-04T06:11:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/StructureDefinition-auditevent-encounter.xlsx
+++ b/currentbuild/StructureDefinition-auditevent-encounter.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3071" uniqueCount="523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3185" uniqueCount="539">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T06:11:20+00:00</t>
+    <t>2024-06-06T18:49:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -745,7 +745,8 @@
     <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
   </si>
   <si>
-    <t>http://hl7.no/fhir/ValueSet/no-basis-encounter-auditevent-servicetype</t>
+    <t xml:space="preserve">value:$this}
+</t>
   </si>
   <si>
     <t>CodeableConcept.coding</t>
@@ -876,6 +877,54 @@
   </si>
   <si>
     <t>Sometimes implied by being first</t>
+  </si>
+  <si>
+    <t>Encounter.serviceType.coding:VOLVEN_8655</t>
+  </si>
+  <si>
+    <t>VOLVEN_8655</t>
+  </si>
+  <si>
+    <t>Volven 8655</t>
+  </si>
+  <si>
+    <t>Helsehjelpsområde (OID=8655)</t>
+  </si>
+  <si>
+    <t>Volven</t>
+  </si>
+  <si>
+    <t>urn:oid:2.16.578.1.12.4.1.1.8655</t>
+  </si>
+  <si>
+    <t>Encounter.serviceType.coding:VOLVEN_8663</t>
+  </si>
+  <si>
+    <t>VOLVEN_8663</t>
+  </si>
+  <si>
+    <t>Volven 8663</t>
+  </si>
+  <si>
+    <t>Tjenestetyper for kommunal helse- og omsorgstjeneste mv. (OID=8663)</t>
+  </si>
+  <si>
+    <t>urn:oid:2.16.578.1.12.4.1.1.8663</t>
+  </si>
+  <si>
+    <t>Encounter.serviceType.coding:VOLVEN_8451</t>
+  </si>
+  <si>
+    <t>VOLVEN_8451</t>
+  </si>
+  <si>
+    <t>Volven 8451</t>
+  </si>
+  <si>
+    <t>Fagområde (OID=8451)</t>
+  </si>
+  <si>
+    <t>urn:oid:2.16.578.1.12.4.1.1.8451</t>
   </si>
   <si>
     <t>Encounter.serviceType.text</t>
@@ -1924,12 +1973,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN85"/>
+  <dimension ref="A1:AN88"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="45.67578125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="45.67578125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="14.12890625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -1952,7 +2001,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="74.65625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="65.01953125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="56.25390625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
@@ -5327,26 +5376,26 @@
         <v>78</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="Y30" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB30" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="AA30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB30" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC30" t="s" s="2">
-        <v>78</v>
-      </c>
+      <c r="AC30" s="2"/>
       <c r="AD30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>78</v>
+        <v>229</v>
       </c>
       <c r="AF30" t="s" s="2">
         <v>236</v>
@@ -6181,9 +6230,11 @@
         <v>279</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="C38" s="2"/>
+        <v>230</v>
+      </c>
+      <c r="C38" t="s" s="2">
+        <v>280</v>
+      </c>
       <c r="D38" t="s" s="2">
         <v>78</v>
       </c>
@@ -6204,19 +6255,19 @@
         <v>87</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>169</v>
+        <v>187</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>282</v>
+        <v>233</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>283</v>
+        <v>234</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>78</v>
@@ -6241,13 +6292,13 @@
         <v>78</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>78</v>
+        <v>155</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>78</v>
+        <v>283</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>78</v>
+        <v>284</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>78</v>
@@ -6265,13 +6316,13 @@
         <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>284</v>
+        <v>236</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>78</v>
@@ -6283,23 +6334,25 @@
         <v>78</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>285</v>
+        <v>237</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>286</v>
+        <v>238</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="C39" s="2"/>
+        <v>230</v>
+      </c>
+      <c r="C39" t="s" s="2">
+        <v>286</v>
+      </c>
       <c r="D39" t="s" s="2">
         <v>78</v>
       </c>
@@ -6317,19 +6370,23 @@
         <v>78</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>209</v>
+        <v>187</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="M39" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="N39" s="2"/>
-      <c r="O39" s="2"/>
+      <c r="N39" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>234</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>78</v>
       </c>
@@ -6353,14 +6410,14 @@
         <v>78</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>213</v>
+        <v>155</v>
       </c>
       <c r="Y39" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="Z39" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="Z39" t="s" s="2">
-        <v>290</v>
-      </c>
       <c r="AA39" t="s" s="2">
         <v>78</v>
       </c>
@@ -6377,13 +6434,13 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>287</v>
+        <v>236</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>78</v>
@@ -6395,25 +6452,27 @@
         <v>78</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>291</v>
+        <v>237</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>292</v>
+        <v>78</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>293</v>
+        <v>238</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="C40" s="2"/>
+        <v>230</v>
+      </c>
+      <c r="C40" t="s" s="2">
+        <v>291</v>
+      </c>
       <c r="D40" t="s" s="2">
-        <v>295</v>
+        <v>78</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6432,18 +6491,20 @@
         <v>87</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>296</v>
+        <v>187</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="O40" s="2"/>
+        <v>233</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>234</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>78</v>
       </c>
@@ -6467,13 +6528,13 @@
         <v>78</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>78</v>
+        <v>155</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>78</v>
+        <v>283</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>78</v>
+        <v>294</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>78</v>
@@ -6491,13 +6552,13 @@
         <v>78</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>294</v>
+        <v>236</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>78</v>
@@ -6506,24 +6567,24 @@
         <v>98</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>300</v>
+        <v>78</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>301</v>
+        <v>237</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>302</v>
+        <v>78</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>303</v>
+        <v>238</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6534,7 +6595,7 @@
         <v>76</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>78</v>
@@ -6546,16 +6607,20 @@
         <v>87</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>305</v>
+        <v>169</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="N41" s="2"/>
-      <c r="O41" s="2"/>
+        <v>297</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>299</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>78</v>
       </c>
@@ -6603,13 +6668,13 @@
         <v>78</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>78</v>
@@ -6618,35 +6683,35 @@
         <v>98</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>308</v>
+        <v>78</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>167</v>
+        <v>301</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>309</v>
+        <v>78</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>310</v>
+        <v>302</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>312</v>
+        <v>78</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>78</v>
@@ -6658,13 +6723,13 @@
         <v>78</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>313</v>
+        <v>209</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6691,13 +6756,13 @@
         <v>78</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>78</v>
+        <v>213</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>78</v>
+        <v>305</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>78</v>
+        <v>306</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>78</v>
@@ -6715,13 +6780,13 @@
         <v>78</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>78</v>
@@ -6730,35 +6795,35 @@
         <v>98</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>316</v>
+        <v>78</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>78</v>
+        <v>308</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>78</v>
+        <v>309</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>78</v>
+        <v>311</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>78</v>
@@ -6770,15 +6835,17 @@
         <v>87</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>163</v>
+        <v>312</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>314</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>315</v>
+      </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>78</v>
@@ -6827,13 +6894,13 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>78</v>
@@ -6842,24 +6909,24 @@
         <v>98</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>78</v>
+        <v>318</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>323</v>
+        <v>319</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6870,7 +6937,7 @@
         <v>76</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>78</v>
@@ -6879,16 +6946,16 @@
         <v>78</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>169</v>
+        <v>321</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>170</v>
+        <v>322</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>171</v>
+        <v>323</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6939,43 +7006,43 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>172</v>
+        <v>320</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>78</v>
+        <v>324</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>167</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>78</v>
+        <v>325</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>78</v>
+        <v>326</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>131</v>
+        <v>328</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -6994,17 +7061,15 @@
         <v>78</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>132</v>
+        <v>329</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>133</v>
+        <v>330</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>135</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>78</v>
@@ -7053,7 +7118,7 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>175</v>
+        <v>327</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>76</v>
@@ -7065,13 +7130,13 @@
         <v>78</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>137</v>
+        <v>98</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>78</v>
+        <v>332</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>167</v>
+        <v>333</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>78</v>
@@ -7082,14 +7147,14 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>177</v>
+        <v>78</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7102,26 +7167,22 @@
         <v>78</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="J46" t="s" s="2">
         <v>87</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>132</v>
+        <v>163</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>178</v>
+        <v>335</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>141</v>
-      </c>
+        <v>336</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>78</v>
       </c>
@@ -7169,7 +7230,7 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>180</v>
+        <v>334</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>76</v>
@@ -7181,27 +7242,27 @@
         <v>78</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>137</v>
+        <v>98</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>78</v>
+        <v>337</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>129</v>
+        <v>338</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>78</v>
+        <v>339</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>327</v>
+        <v>340</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>327</v>
+        <v>340</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7212,7 +7273,7 @@
         <v>76</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>78</v>
@@ -7221,20 +7282,18 @@
         <v>78</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>209</v>
+        <v>169</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>328</v>
+        <v>170</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>330</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>78</v>
@@ -7259,13 +7318,13 @@
         <v>78</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>190</v>
+        <v>78</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>329</v>
+        <v>78</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>331</v>
+        <v>78</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>78</v>
@@ -7283,50 +7342,50 @@
         <v>78</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>327</v>
+        <v>172</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>332</v>
+        <v>78</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>333</v>
+        <v>167</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>334</v>
+        <v>78</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>78</v>
+        <v>131</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>78</v>
@@ -7338,15 +7397,17 @@
         <v>78</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>183</v>
+        <v>132</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>336</v>
+        <v>133</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="N48" s="2"/>
+        <v>174</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>135</v>
+      </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>78</v>
@@ -7395,71 +7456,75 @@
         <v>78</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>335</v>
+        <v>175</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>338</v>
+        <v>167</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>339</v>
+        <v>78</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>78</v>
+        <v>177</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="J49" t="s" s="2">
         <v>87</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>341</v>
+        <v>132</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>342</v>
+        <v>178</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="N49" s="2"/>
-      <c r="O49" s="2"/>
+        <v>179</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="O49" t="s" s="2">
+        <v>141</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>78</v>
       </c>
@@ -7507,39 +7572,39 @@
         <v>78</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>340</v>
+        <v>180</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>344</v>
+        <v>78</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>345</v>
+        <v>129</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>346</v>
+        <v>78</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>347</v>
+        <v>78</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7562,15 +7627,17 @@
         <v>87</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>349</v>
+        <v>209</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>345</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>346</v>
+      </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>78</v>
@@ -7595,13 +7662,13 @@
         <v>78</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>78</v>
+        <v>190</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>78</v>
+        <v>345</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>78</v>
+        <v>347</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>78</v>
@@ -7619,7 +7686,7 @@
         <v>78</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>76</v>
@@ -7634,24 +7701,24 @@
         <v>98</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>316</v>
+        <v>348</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>353</v>
+        <v>350</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7677,14 +7744,12 @@
         <v>183</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>357</v>
-      </c>
+        <v>353</v>
+      </c>
+      <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>78</v>
@@ -7733,7 +7798,7 @@
         <v>78</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>76</v>
@@ -7748,24 +7813,24 @@
         <v>98</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>358</v>
+        <v>78</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>360</v>
+        <v>78</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>361</v>
+        <v>355</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7785,20 +7850,18 @@
         <v>78</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>366</v>
-      </c>
+        <v>359</v>
+      </c>
+      <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>78</v>
@@ -7847,7 +7910,7 @@
         <v>78</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>76</v>
@@ -7862,28 +7925,28 @@
         <v>98</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>78</v>
+        <v>362</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>368</v>
+        <v>363</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>370</v>
+        <v>78</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -7902,17 +7965,15 @@
         <v>87</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>209</v>
+        <v>365</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>373</v>
-      </c>
+        <v>367</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>78</v>
@@ -7937,13 +7998,13 @@
         <v>78</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>374</v>
+        <v>78</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>375</v>
+        <v>78</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>78</v>
@@ -7961,7 +8022,7 @@
         <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>76</v>
@@ -7976,35 +8037,35 @@
         <v>98</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>376</v>
+        <v>332</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>377</v>
+        <v>368</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>378</v>
+        <v>78</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>379</v>
+        <v>369</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>370</v>
+        <v>78</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>78</v>
@@ -8013,13 +8074,13 @@
         <v>78</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>381</v>
+        <v>183</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>382</v>
+        <v>371</v>
       </c>
       <c r="M54" t="s" s="2">
         <v>372</v>
@@ -8075,13 +8136,13 @@
         <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>78</v>
@@ -8090,24 +8151,24 @@
         <v>98</v>
       </c>
       <c r="AK54" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="AM54" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="AL54" t="s" s="2">
+      <c r="AN54" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="AM54" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>379</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8118,7 +8179,7 @@
         <v>76</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>78</v>
@@ -8127,18 +8188,20 @@
         <v>78</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>163</v>
+        <v>379</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="N55" s="2"/>
+        <v>381</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>382</v>
+      </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>78</v>
@@ -8187,13 +8250,13 @@
         <v>78</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>78</v>
@@ -8202,35 +8265,35 @@
         <v>98</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>78</v>
+        <v>374</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>78</v>
+        <v>384</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>78</v>
+        <v>386</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>78</v>
@@ -8239,18 +8302,20 @@
         <v>78</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>169</v>
+        <v>209</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>170</v>
+        <v>387</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>388</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>389</v>
+      </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>78</v>
@@ -8275,13 +8340,13 @@
         <v>78</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>78</v>
+        <v>390</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>78</v>
+        <v>391</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>78</v>
@@ -8299,43 +8364,43 @@
         <v>78</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>172</v>
+        <v>385</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>78</v>
+        <v>392</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>167</v>
+        <v>393</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>78</v>
+        <v>394</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>78</v>
+        <v>395</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>131</v>
+        <v>386</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8351,19 +8416,19 @@
         <v>78</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>132</v>
+        <v>397</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>133</v>
+        <v>398</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>174</v>
+        <v>388</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>135</v>
+        <v>389</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8413,7 +8478,7 @@
         <v>78</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>175</v>
+        <v>396</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>76</v>
@@ -8425,31 +8490,31 @@
         <v>78</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>137</v>
+        <v>98</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>78</v>
+        <v>392</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>167</v>
+        <v>393</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>78</v>
+        <v>394</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>78</v>
+        <v>395</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>389</v>
+        <v>399</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>389</v>
+        <v>399</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>177</v>
+        <v>78</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8462,26 +8527,22 @@
         <v>78</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="J58" t="s" s="2">
         <v>87</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>132</v>
+        <v>163</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>178</v>
+        <v>400</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>141</v>
-      </c>
+        <v>401</v>
+      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>78</v>
       </c>
@@ -8529,7 +8590,7 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>180</v>
+        <v>399</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>76</v>
@@ -8541,13 +8602,13 @@
         <v>78</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>137</v>
+        <v>98</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>129</v>
+        <v>402</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>78</v>
@@ -8558,18 +8619,18 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>390</v>
+        <v>403</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>390</v>
+        <v>403</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>391</v>
+        <v>78</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="G59" t="s" s="2">
         <v>86</v>
@@ -8581,20 +8642,18 @@
         <v>78</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>392</v>
+        <v>169</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>393</v>
+        <v>170</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>373</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="N59" s="2"/>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>78</v>
@@ -8643,10 +8702,10 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>390</v>
+        <v>172</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="AH59" t="s" s="2">
         <v>86</v>
@@ -8655,38 +8714,38 @@
         <v>78</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>395</v>
+        <v>78</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>396</v>
+        <v>167</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>378</v>
+        <v>78</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>397</v>
+        <v>78</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>78</v>
+        <v>131</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>78</v>
@@ -8698,15 +8757,17 @@
         <v>78</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>209</v>
+        <v>132</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>399</v>
+        <v>133</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="N60" s="2"/>
+        <v>174</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>135</v>
+      </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>78</v>
@@ -8731,13 +8792,13 @@
         <v>78</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>401</v>
+        <v>78</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>402</v>
+        <v>78</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>78</v>
@@ -8755,19 +8816,19 @@
         <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>398</v>
+        <v>175</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>78</v>
@@ -8784,42 +8845,46 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>78</v>
+        <v>177</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I61" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>404</v>
+        <v>132</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>405</v>
+        <v>178</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="N61" s="2"/>
-      <c r="O61" s="2"/>
+        <v>179</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>141</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>78</v>
       </c>
@@ -8867,25 +8932,25 @@
         <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>403</v>
+        <v>180</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>407</v>
+        <v>129</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>78</v>
@@ -8896,21 +8961,21 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>78</v>
+        <v>407</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>78</v>
@@ -8919,19 +8984,19 @@
         <v>78</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="L62" t="s" s="2">
         <v>409</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="M62" t="s" s="2">
         <v>410</v>
       </c>
-      <c r="M62" t="s" s="2">
-        <v>411</v>
-      </c>
       <c r="N62" t="s" s="2">
-        <v>412</v>
+        <v>389</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -8981,13 +9046,13 @@
         <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>78</v>
@@ -8996,16 +9061,16 @@
         <v>98</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>78</v>
+        <v>411</v>
       </c>
       <c r="AL62" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="AN62" t="s" s="2">
         <v>413</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AN62" t="s" s="2">
-        <v>78</v>
       </c>
     </row>
     <row r="63">
@@ -9036,7 +9101,7 @@
         <v>78</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>163</v>
+        <v>209</v>
       </c>
       <c r="L63" t="s" s="2">
         <v>415</v>
@@ -9044,9 +9109,7 @@
       <c r="M63" t="s" s="2">
         <v>416</v>
       </c>
-      <c r="N63" t="s" s="2">
-        <v>417</v>
-      </c>
+      <c r="N63" s="2"/>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>78</v>
@@ -9071,13 +9134,13 @@
         <v>78</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>78</v>
+        <v>417</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>78</v>
+        <v>418</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>78</v>
@@ -9113,7 +9176,7 @@
         <v>78</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>418</v>
+        <v>167</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>78</v>
@@ -9150,13 +9213,13 @@
         <v>78</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>169</v>
+        <v>420</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>170</v>
+        <v>421</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>171</v>
+        <v>422</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9207,7 +9270,7 @@
         <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>172</v>
+        <v>419</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>76</v>
@@ -9219,13 +9282,13 @@
         <v>78</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>167</v>
+        <v>423</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>78</v>
@@ -9236,14 +9299,14 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>131</v>
+        <v>78</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -9262,16 +9325,16 @@
         <v>78</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>132</v>
+        <v>425</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>133</v>
+        <v>426</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>174</v>
+        <v>427</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>135</v>
+        <v>428</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9321,7 +9384,7 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>175</v>
+        <v>424</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>76</v>
@@ -9333,13 +9396,13 @@
         <v>78</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>137</v>
+        <v>98</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>167</v>
+        <v>429</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>78</v>
@@ -9350,46 +9413,44 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>177</v>
+        <v>78</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>132</v>
+        <v>163</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>178</v>
+        <v>431</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>179</v>
+        <v>432</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>141</v>
-      </c>
+        <v>433</v>
+      </c>
+      <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>78</v>
       </c>
@@ -9437,25 +9498,25 @@
         <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>180</v>
+        <v>430</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>137</v>
+        <v>98</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>129</v>
+        <v>434</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>78</v>
@@ -9466,10 +9527,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>422</v>
+        <v>435</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>422</v>
+        <v>435</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9492,13 +9553,13 @@
         <v>78</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>144</v>
+        <v>169</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>423</v>
+        <v>170</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>424</v>
+        <v>171</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9549,7 +9610,7 @@
         <v>78</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>422</v>
+        <v>172</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>76</v>
@@ -9561,38 +9622,38 @@
         <v>78</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>148</v>
+        <v>167</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>425</v>
+        <v>78</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>78</v>
+        <v>131</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>78</v>
@@ -9604,15 +9665,17 @@
         <v>78</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>427</v>
+        <v>132</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>428</v>
+        <v>133</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="N68" s="2"/>
+        <v>174</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>135</v>
+      </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>78</v>
@@ -9661,25 +9724,25 @@
         <v>78</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>426</v>
+        <v>175</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>430</v>
+        <v>167</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>78</v>
@@ -9690,42 +9753,46 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>78</v>
+        <v>177</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I69" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>209</v>
+        <v>132</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>432</v>
+        <v>178</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="N69" s="2"/>
-      <c r="O69" s="2"/>
+        <v>179</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>141</v>
+      </c>
       <c r="P69" t="s" s="2">
         <v>78</v>
       </c>
@@ -9749,13 +9816,13 @@
         <v>78</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>434</v>
+        <v>78</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>435</v>
+        <v>78</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>78</v>
@@ -9773,31 +9840,31 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>431</v>
+        <v>180</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>436</v>
+        <v>129</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>437</v>
+        <v>78</v>
       </c>
     </row>
     <row r="70">
@@ -9828,7 +9895,7 @@
         <v>78</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>209</v>
+        <v>144</v>
       </c>
       <c r="L70" t="s" s="2">
         <v>439</v>
@@ -9861,13 +9928,13 @@
         <v>78</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>213</v>
+        <v>78</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>441</v>
+        <v>78</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>442</v>
+        <v>78</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>78</v>
@@ -9903,21 +9970,21 @@
         <v>78</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>167</v>
+        <v>148</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9928,7 +9995,7 @@
         <v>76</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>78</v>
@@ -9940,20 +10007,16 @@
         <v>78</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>209</v>
+        <v>443</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>445</v>
       </c>
-      <c r="M71" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>448</v>
-      </c>
+      <c r="N71" s="2"/>
+      <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>78</v>
       </c>
@@ -9977,13 +10040,13 @@
         <v>78</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>213</v>
+        <v>78</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>449</v>
+        <v>78</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>450</v>
+        <v>78</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>78</v>
@@ -10001,13 +10064,13 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>78</v>
@@ -10019,21 +10082,21 @@
         <v>78</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>452</v>
+        <v>78</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10044,7 +10107,7 @@
         <v>76</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>78</v>
@@ -10059,10 +10122,10 @@
         <v>209</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10092,10 +10155,10 @@
         <v>110</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>78</v>
@@ -10113,13 +10176,13 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>78</v>
@@ -10131,21 +10194,21 @@
         <v>78</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>459</v>
+        <v>453</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10156,7 +10219,7 @@
         <v>76</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>78</v>
@@ -10171,10 +10234,10 @@
         <v>209</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10201,13 +10264,13 @@
         <v>78</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>110</v>
+        <v>213</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>78</v>
@@ -10225,13 +10288,13 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>78</v>
@@ -10243,21 +10306,21 @@
         <v>78</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>465</v>
+        <v>167</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>466</v>
+        <v>459</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>467</v>
+        <v>460</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>467</v>
+        <v>460</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10268,7 +10331,7 @@
         <v>76</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>78</v>
@@ -10280,16 +10343,20 @@
         <v>78</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>427</v>
+        <v>209</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="N74" s="2"/>
-      <c r="O74" s="2"/>
+        <v>462</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="O74" t="s" s="2">
+        <v>464</v>
+      </c>
       <c r="P74" t="s" s="2">
         <v>78</v>
       </c>
@@ -10313,13 +10380,13 @@
         <v>78</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>78</v>
+        <v>213</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>78</v>
+        <v>465</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>78</v>
+        <v>466</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>78</v>
@@ -10337,13 +10404,13 @@
         <v>78</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>467</v>
+        <v>460</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>78</v>
@@ -10355,21 +10422,21 @@
         <v>78</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>471</v>
+        <v>468</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10380,7 +10447,7 @@
         <v>76</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>78</v>
@@ -10395,10 +10462,10 @@
         <v>209</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -10425,13 +10492,13 @@
         <v>78</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>213</v>
+        <v>110</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>78</v>
@@ -10449,13 +10516,13 @@
         <v>78</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>78</v>
@@ -10467,21 +10534,21 @@
         <v>78</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>478</v>
+        <v>475</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10504,17 +10571,15 @@
         <v>78</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>163</v>
+        <v>209</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>482</v>
-      </c>
+        <v>478</v>
+      </c>
+      <c r="N76" s="2"/>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>78</v>
@@ -10539,13 +10604,13 @@
         <v>78</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>78</v>
+        <v>479</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>78</v>
+        <v>480</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>78</v>
@@ -10563,7 +10628,7 @@
         <v>78</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>76</v>
@@ -10581,21 +10646,21 @@
         <v>78</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>78</v>
+        <v>482</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10618,13 +10683,13 @@
         <v>78</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>169</v>
+        <v>443</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>170</v>
+        <v>484</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>171</v>
+        <v>485</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -10675,7 +10740,7 @@
         <v>78</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>172</v>
+        <v>483</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>76</v>
@@ -10687,38 +10752,38 @@
         <v>78</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>167</v>
+        <v>486</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>78</v>
+        <v>487</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>131</v>
+        <v>78</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>78</v>
@@ -10730,17 +10795,15 @@
         <v>78</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>132</v>
+        <v>209</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>133</v>
+        <v>489</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>135</v>
-      </c>
+        <v>490</v>
+      </c>
+      <c r="N78" s="2"/>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>78</v>
@@ -10765,13 +10828,13 @@
         <v>78</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>78</v>
+        <v>213</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>78</v>
+        <v>491</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>78</v>
+        <v>492</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>78</v>
@@ -10789,43 +10852,43 @@
         <v>78</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>175</v>
+        <v>488</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>137</v>
+        <v>98</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>167</v>
+        <v>493</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>78</v>
+        <v>494</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>486</v>
+        <v>495</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>486</v>
+        <v>495</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>177</v>
+        <v>78</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
@@ -10838,26 +10901,24 @@
         <v>78</v>
       </c>
       <c r="I79" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>132</v>
+        <v>163</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>178</v>
+        <v>496</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>179</v>
+        <v>497</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="O79" t="s" s="2">
-        <v>141</v>
-      </c>
+        <v>498</v>
+      </c>
+      <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>78</v>
       </c>
@@ -10905,7 +10966,7 @@
         <v>78</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>180</v>
+        <v>495</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>76</v>
@@ -10917,13 +10978,13 @@
         <v>78</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>137</v>
+        <v>98</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>129</v>
+        <v>499</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>78</v>
@@ -10934,10 +10995,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>487</v>
+        <v>500</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>487</v>
+        <v>500</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10945,7 +11006,7 @@
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="G80" t="s" s="2">
         <v>86</v>
@@ -10960,13 +11021,13 @@
         <v>78</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>488</v>
+        <v>169</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>489</v>
+        <v>170</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>490</v>
+        <v>171</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11017,10 +11078,10 @@
         <v>78</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>487</v>
+        <v>172</v>
       </c>
       <c r="AG80" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="AH80" t="s" s="2">
         <v>86</v>
@@ -11029,38 +11090,38 @@
         <v>78</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>491</v>
+        <v>78</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>345</v>
+        <v>167</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>492</v>
+        <v>78</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>493</v>
+        <v>78</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>494</v>
+        <v>501</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>494</v>
+        <v>501</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>78</v>
+        <v>131</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>78</v>
@@ -11072,16 +11133,16 @@
         <v>78</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>106</v>
+        <v>132</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>495</v>
+        <v>133</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>496</v>
+        <v>174</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>497</v>
+        <v>135</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11107,13 +11168,13 @@
         <v>78</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>155</v>
+        <v>78</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>498</v>
+        <v>78</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>499</v>
+        <v>78</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>78</v>
@@ -11131,25 +11192,25 @@
         <v>78</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>494</v>
+        <v>175</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>500</v>
+        <v>167</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>78</v>
@@ -11160,44 +11221,46 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>78</v>
+        <v>177</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I82" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>209</v>
+        <v>132</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>502</v>
+        <v>178</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>503</v>
+        <v>179</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="O82" s="2"/>
+        <v>135</v>
+      </c>
+      <c r="O82" t="s" s="2">
+        <v>141</v>
+      </c>
       <c r="P82" t="s" s="2">
         <v>78</v>
       </c>
@@ -11221,13 +11284,13 @@
         <v>78</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>213</v>
+        <v>78</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>505</v>
+        <v>78</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>506</v>
+        <v>78</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>78</v>
@@ -11245,25 +11308,25 @@
         <v>78</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>501</v>
+        <v>180</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>78</v>
+        <v>129</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>78</v>
@@ -11274,10 +11337,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11285,7 +11348,7 @@
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="G83" t="s" s="2">
         <v>86</v>
@@ -11300,13 +11363,13 @@
         <v>78</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>183</v>
+        <v>504</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -11357,10 +11420,10 @@
         <v>78</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="AG83" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="AH83" t="s" s="2">
         <v>86</v>
@@ -11372,16 +11435,16 @@
         <v>98</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>78</v>
+        <v>507</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>338</v>
+        <v>361</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>78</v>
+        <v>508</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>78</v>
+        <v>509</v>
       </c>
     </row>
     <row r="84">
@@ -11412,15 +11475,17 @@
         <v>78</v>
       </c>
       <c r="K84" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="L84" t="s" s="2">
         <v>511</v>
       </c>
-      <c r="L84" t="s" s="2">
+      <c r="M84" t="s" s="2">
         <v>512</v>
       </c>
-      <c r="M84" t="s" s="2">
+      <c r="N84" t="s" s="2">
         <v>513</v>
       </c>
-      <c r="N84" s="2"/>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>78</v>
@@ -11445,13 +11510,13 @@
         <v>78</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>78</v>
+        <v>155</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>78</v>
+        <v>514</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>78</v>
+        <v>515</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>78</v>
@@ -11484,24 +11549,24 @@
         <v>98</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>344</v>
+        <v>78</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>515</v>
+        <v>78</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11524,7 +11589,7 @@
         <v>78</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>517</v>
+        <v>209</v>
       </c>
       <c r="L85" t="s" s="2">
         <v>518</v>
@@ -11559,13 +11624,13 @@
         <v>78</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>78</v>
+        <v>213</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>78</v>
+        <v>521</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>78</v>
+        <v>522</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>78</v>
@@ -11583,7 +11648,7 @@
         <v>78</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>76</v>
@@ -11598,15 +11663,353 @@
         <v>98</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>521</v>
+        <v>78</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>522</v>
+        <v>78</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN85" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="B86" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="C86" s="2"/>
+      <c r="D86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E86" s="2"/>
+      <c r="F86" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G86" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K86" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="L86" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="M86" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="N86" s="2"/>
+      <c r="O86" s="2"/>
+      <c r="P86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q86" s="2"/>
+      <c r="R86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF86" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="AG86" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH86" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ86" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL86" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="AM86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN86" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="B87" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="C87" s="2"/>
+      <c r="D87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E87" s="2"/>
+      <c r="F87" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G87" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K87" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="L87" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="M87" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="N87" s="2"/>
+      <c r="O87" s="2"/>
+      <c r="P87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q87" s="2"/>
+      <c r="R87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF87" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="AG87" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH87" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ87" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK87" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="AL87" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="AM87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN87" t="s" s="2">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="B88" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="C88" s="2"/>
+      <c r="D88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E88" s="2"/>
+      <c r="F88" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G88" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K88" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="L88" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="M88" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="N88" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="O88" s="2"/>
+      <c r="P88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q88" s="2"/>
+      <c r="R88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF88" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="AG88" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH88" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ88" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK88" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="AL88" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="AM88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN88" t="s" s="2">
         <v>78</v>
       </c>
     </row>
